--- a/EndlessGuildExporter/Endless-Legion-Roster.xlsx
+++ b/EndlessGuildExporter/Endless-Legion-Roster.xlsx
@@ -10,7 +10,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="15">
+  <fonts count="14">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -97,14 +97,8 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
   </fonts>
-  <fills count="16">
+  <fills count="15">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -132,12 +126,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFF7C0A"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF33937F"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -210,7 +198,7 @@
       <alignment horizontal="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -253,9 +241,6 @@
     <xf numFmtId="0" fontId="13" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -341,7 +326,7 @@
           <t>Diaara</t>
         </is>
       </c>
-      <c r="B2" s="13" t="inlineStr">
+      <c r="B2" s="12" t="inlineStr">
         <is>
           <t>Warlock</t>
         </is>
@@ -407,7 +392,7 @@
           <t>Asdadqqasd</t>
         </is>
       </c>
-      <c r="B3" s="8" t="inlineStr">
+      <c r="B3" s="7" t="inlineStr">
         <is>
           <t>Monk</t>
         </is>
@@ -473,7 +458,7 @@
           <t>Wazx</t>
         </is>
       </c>
-      <c r="B4" s="12" t="inlineStr">
+      <c r="B4" s="11" t="inlineStr">
         <is>
           <t>Shaman</t>
         </is>
@@ -539,7 +524,7 @@
           <t>Xyhopriest</t>
         </is>
       </c>
-      <c r="B5" s="10" t="inlineStr">
+      <c r="B5" s="9" t="inlineStr">
         <is>
           <t>Priest</t>
         </is>
@@ -571,12 +556,12 @@
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
-          <t>Evoker</t>
+          <t>Hunter</t>
         </is>
       </c>
       <c r="I5">
-        <f>SUMPRODUCT(--($B$2:$B$230="Evoker"),--(COUNTIFS($K$2:$K$10,$F$2:$F$230,$M$2:$M$10,"☑")&gt;0))</f>
-        <v>0</v>
+        <f>SUMPRODUCT(--($B$2:$B$230="Hunter"),--(COUNTIFS($K$2:$K$10,$F$2:$F$230,$M$2:$M$10,"☑")&gt;0))</f>
+        <v>15</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -637,12 +622,12 @@
       </c>
       <c r="H6" s="6" t="inlineStr">
         <is>
-          <t>Hunter</t>
+          <t>Mage</t>
         </is>
       </c>
       <c r="I6">
-        <f>SUMPRODUCT(--($B$2:$B$230="Hunter"),--(COUNTIFS($K$2:$K$10,$F$2:$F$230,$M$2:$M$10,"☑")&gt;0))</f>
-        <v>15</v>
+        <f>SUMPRODUCT(--($B$2:$B$230="Mage"),--(COUNTIFS($K$2:$K$10,$F$2:$F$230,$M$2:$M$10,"☑")&gt;0))</f>
+        <v>26</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -671,7 +656,7 @@
           <t>Mygfishot</t>
         </is>
       </c>
-      <c r="B7" s="14" t="inlineStr">
+      <c r="B7" s="13" t="inlineStr">
         <is>
           <t>Warrior</t>
         </is>
@@ -703,12 +688,12 @@
       </c>
       <c r="H7" s="7" t="inlineStr">
         <is>
-          <t>Mage</t>
+          <t>Monk</t>
         </is>
       </c>
       <c r="I7">
-        <f>SUMPRODUCT(--($B$2:$B$230="Mage"),--(COUNTIFS($K$2:$K$10,$F$2:$F$230,$M$2:$M$10,"☑")&gt;0))</f>
-        <v>26</v>
+        <f>SUMPRODUCT(--($B$2:$B$230="Monk"),--(COUNTIFS($K$2:$K$10,$F$2:$F$230,$M$2:$M$10,"☑")&gt;0))</f>
+        <v>24</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -769,12 +754,12 @@
       </c>
       <c r="H8" s="8" t="inlineStr">
         <is>
-          <t>Monk</t>
+          <t>Paladin</t>
         </is>
       </c>
       <c r="I8">
-        <f>SUMPRODUCT(--($B$2:$B$230="Monk"),--(COUNTIFS($K$2:$K$10,$F$2:$F$230,$M$2:$M$10,"☑")&gt;0))</f>
-        <v>24</v>
+        <f>SUMPRODUCT(--($B$2:$B$230="Paladin"),--(COUNTIFS($K$2:$K$10,$F$2:$F$230,$M$2:$M$10,"☑")&gt;0))</f>
+        <v>15</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -835,12 +820,12 @@
       </c>
       <c r="H9" s="9" t="inlineStr">
         <is>
-          <t>Paladin</t>
+          <t>Priest</t>
         </is>
       </c>
       <c r="I9">
-        <f>SUMPRODUCT(--($B$2:$B$230="Paladin"),--(COUNTIFS($K$2:$K$10,$F$2:$F$230,$M$2:$M$10,"☑")&gt;0))</f>
-        <v>15</v>
+        <f>SUMPRODUCT(--($B$2:$B$230="Priest"),--(COUNTIFS($K$2:$K$10,$F$2:$F$230,$M$2:$M$10,"☑")&gt;0))</f>
+        <v>21</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -869,7 +854,7 @@
           <t>Goodinbed</t>
         </is>
       </c>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B10" s="6" t="inlineStr">
         <is>
           <t>Mage</t>
         </is>
@@ -901,12 +886,12 @@
       </c>
       <c r="H10" s="10" t="inlineStr">
         <is>
-          <t>Priest</t>
+          <t>Rogue</t>
         </is>
       </c>
       <c r="I10">
-        <f>SUMPRODUCT(--($B$2:$B$230="Priest"),--(COUNTIFS($K$2:$K$10,$F$2:$F$230,$M$2:$M$10,"☑")&gt;0))</f>
-        <v>21</v>
+        <f>SUMPRODUCT(--($B$2:$B$230="Rogue"),--(COUNTIFS($K$2:$K$10,$F$2:$F$230,$M$2:$M$10,"☑")&gt;0))</f>
+        <v>14</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -935,7 +920,7 @@
           <t>Lnfour</t>
         </is>
       </c>
-      <c r="B11" s="13" t="inlineStr">
+      <c r="B11" s="12" t="inlineStr">
         <is>
           <t>Warlock</t>
         </is>
@@ -967,12 +952,12 @@
       </c>
       <c r="H11" s="11" t="inlineStr">
         <is>
-          <t>Rogue</t>
+          <t>Shaman</t>
         </is>
       </c>
       <c r="I11">
-        <f>SUMPRODUCT(--($B$2:$B$230="Rogue"),--(COUNTIFS($K$2:$K$10,$F$2:$F$230,$M$2:$M$10,"☑")&gt;0))</f>
-        <v>14</v>
+        <f>SUMPRODUCT(--($B$2:$B$230="Shaman"),--(COUNTIFS($K$2:$K$10,$F$2:$F$230,$M$2:$M$10,"☑")&gt;0))</f>
+        <v>19</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -1001,7 +986,7 @@
           <t>Nakedchefx</t>
         </is>
       </c>
-      <c r="B12" s="12" t="inlineStr">
+      <c r="B12" s="11" t="inlineStr">
         <is>
           <t>Shaman</t>
         </is>
@@ -1033,11 +1018,11 @@
       </c>
       <c r="H12" s="12" t="inlineStr">
         <is>
-          <t>Shaman</t>
+          <t>Warlock</t>
         </is>
       </c>
       <c r="I12">
-        <f>SUMPRODUCT(--($B$2:$B$230="Shaman"),--(COUNTIFS($K$2:$K$10,$F$2:$F$230,$M$2:$M$10,"☑")&gt;0))</f>
+        <f>SUMPRODUCT(--($B$2:$B$230="Warlock"),--(COUNTIFS($K$2:$K$10,$F$2:$F$230,$M$2:$M$10,"☑")&gt;0))</f>
         <v>19</v>
       </c>
       <c r="J12" t="inlineStr">
@@ -1099,12 +1084,12 @@
       </c>
       <c r="H13" s="13" t="inlineStr">
         <is>
-          <t>Warlock</t>
+          <t>Warrior</t>
         </is>
       </c>
       <c r="I13">
-        <f>SUMPRODUCT(--($B$2:$B$230="Warlock"),--(COUNTIFS($K$2:$K$10,$F$2:$F$230,$M$2:$M$10,"☑")&gt;0))</f>
-        <v>19</v>
+        <f>SUMPRODUCT(--($B$2:$B$230="Warrior"),--(COUNTIFS($K$2:$K$10,$F$2:$F$230,$M$2:$M$10,"☑")&gt;0))</f>
+        <v>20</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1133,7 +1118,7 @@
           <t>Wzshamx</t>
         </is>
       </c>
-      <c r="B14" s="12" t="inlineStr">
+      <c r="B14" s="11" t="inlineStr">
         <is>
           <t>Shaman</t>
         </is>
@@ -1163,14 +1148,15 @@
           <t/>
         </is>
       </c>
-      <c r="H14" s="14" t="inlineStr">
-        <is>
-          <t>Warrior</t>
-        </is>
-      </c>
-      <c r="I14">
-        <f>SUMPRODUCT(--($B$2:$B$230="Warrior"),--(COUNTIFS($K$2:$K$10,$F$2:$F$230,$M$2:$M$10,"☑")&gt;0))</f>
-        <v>20</v>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -1199,7 +1185,7 @@
           <t>Wzshxmx</t>
         </is>
       </c>
-      <c r="B15" s="12" t="inlineStr">
+      <c r="B15" s="11" t="inlineStr">
         <is>
           <t>Shaman</t>
         </is>
@@ -1266,7 +1252,7 @@
           <t>Wzw</t>
         </is>
       </c>
-      <c r="B16" s="14" t="inlineStr">
+      <c r="B16" s="13" t="inlineStr">
         <is>
           <t>Warrior</t>
         </is>
@@ -1333,7 +1319,7 @@
           <t>Xyhop</t>
         </is>
       </c>
-      <c r="B17" s="8" t="inlineStr">
+      <c r="B17" s="7" t="inlineStr">
         <is>
           <t>Monk</t>
         </is>
@@ -1400,7 +1386,7 @@
           <t>Xyhopaladin</t>
         </is>
       </c>
-      <c r="B18" s="9" t="inlineStr">
+      <c r="B18" s="8" t="inlineStr">
         <is>
           <t>Paladin</t>
         </is>
@@ -1668,7 +1654,7 @@
           <t>Xyhopfour</t>
         </is>
       </c>
-      <c r="B22" s="8" t="inlineStr">
+      <c r="B22" s="7" t="inlineStr">
         <is>
           <t>Monk</t>
         </is>
@@ -1735,7 +1721,7 @@
           <t>Xyhophunter</t>
         </is>
       </c>
-      <c r="B23" s="6" t="inlineStr">
+      <c r="B23" s="5" t="inlineStr">
         <is>
           <t>Hunter</t>
         </is>
@@ -1802,7 +1788,7 @@
           <t>Xyhopmage</t>
         </is>
       </c>
-      <c r="B24" s="7" t="inlineStr">
+      <c r="B24" s="6" t="inlineStr">
         <is>
           <t>Mage</t>
         </is>
@@ -1869,7 +1855,7 @@
           <t>Xyhoprogue</t>
         </is>
       </c>
-      <c r="B25" s="11" t="inlineStr">
+      <c r="B25" s="10" t="inlineStr">
         <is>
           <t>Rogue</t>
         </is>
@@ -1936,7 +1922,7 @@
           <t>Xyhopshaman</t>
         </is>
       </c>
-      <c r="B26" s="12" t="inlineStr">
+      <c r="B26" s="11" t="inlineStr">
         <is>
           <t>Shaman</t>
         </is>
@@ -2003,7 +1989,7 @@
           <t>Xyhopthree</t>
         </is>
       </c>
-      <c r="B27" s="8" t="inlineStr">
+      <c r="B27" s="7" t="inlineStr">
         <is>
           <t>Monk</t>
         </is>
@@ -2070,7 +2056,7 @@
           <t>Xyhoptwo</t>
         </is>
       </c>
-      <c r="B28" s="8" t="inlineStr">
+      <c r="B28" s="7" t="inlineStr">
         <is>
           <t>Monk</t>
         </is>
@@ -2137,7 +2123,7 @@
           <t>Xyhopwarlock</t>
         </is>
       </c>
-      <c r="B29" s="13" t="inlineStr">
+      <c r="B29" s="12" t="inlineStr">
         <is>
           <t>Warlock</t>
         </is>
@@ -2204,7 +2190,7 @@
           <t>Xyhopwarrior</t>
         </is>
       </c>
-      <c r="B30" s="14" t="inlineStr">
+      <c r="B30" s="13" t="inlineStr">
         <is>
           <t>Warrior</t>
         </is>
@@ -2271,7 +2257,7 @@
           <t>Zerobaka</t>
         </is>
       </c>
-      <c r="B31" s="14" t="inlineStr">
+      <c r="B31" s="13" t="inlineStr">
         <is>
           <t>Warrior</t>
         </is>
@@ -2338,7 +2324,7 @@
           <t>Zerolash</t>
         </is>
       </c>
-      <c r="B32" s="12" t="inlineStr">
+      <c r="B32" s="11" t="inlineStr">
         <is>
           <t>Shaman</t>
         </is>
@@ -2472,7 +2458,7 @@
           <t>Zerolul</t>
         </is>
       </c>
-      <c r="B34" s="10" t="inlineStr">
+      <c r="B34" s="9" t="inlineStr">
         <is>
           <t>Priest</t>
         </is>
@@ -2539,7 +2525,7 @@
           <t>Zerolulq</t>
         </is>
       </c>
-      <c r="B35" s="10" t="inlineStr">
+      <c r="B35" s="9" t="inlineStr">
         <is>
           <t>Priest</t>
         </is>
@@ -2740,7 +2726,7 @@
           <t>Пиво</t>
         </is>
       </c>
-      <c r="B38" s="8" t="inlineStr">
+      <c r="B38" s="7" t="inlineStr">
         <is>
           <t>Monk</t>
         </is>
@@ -2807,7 +2793,7 @@
           <t>Darkpaladino</t>
         </is>
       </c>
-      <c r="B39" s="9" t="inlineStr">
+      <c r="B39" s="8" t="inlineStr">
         <is>
           <t>Paladin</t>
         </is>
@@ -2874,7 +2860,7 @@
           <t>Dazerx</t>
         </is>
       </c>
-      <c r="B40" s="14" t="inlineStr">
+      <c r="B40" s="13" t="inlineStr">
         <is>
           <t>Warrior</t>
         </is>
@@ -2941,7 +2927,7 @@
           <t>Hesxng</t>
         </is>
       </c>
-      <c r="B41" s="7" t="inlineStr">
+      <c r="B41" s="6" t="inlineStr">
         <is>
           <t>Mage</t>
         </is>
@@ -3008,7 +2994,7 @@
           <t>Imerik</t>
         </is>
       </c>
-      <c r="B42" s="14" t="inlineStr">
+      <c r="B42" s="13" t="inlineStr">
         <is>
           <t>Warrior</t>
         </is>
@@ -3142,7 +3128,7 @@
           <t>Rxba</t>
         </is>
       </c>
-      <c r="B44" s="9" t="inlineStr">
+      <c r="B44" s="8" t="inlineStr">
         <is>
           <t>Paladin</t>
         </is>
@@ -3209,7 +3195,7 @@
           <t>Skogstokig</t>
         </is>
       </c>
-      <c r="B45" s="10" t="inlineStr">
+      <c r="B45" s="9" t="inlineStr">
         <is>
           <t>Priest</t>
         </is>
@@ -3276,7 +3262,7 @@
           <t>Sundäy</t>
         </is>
       </c>
-      <c r="B46" s="9" t="inlineStr">
+      <c r="B46" s="8" t="inlineStr">
         <is>
           <t>Paladin</t>
         </is>
@@ -3343,7 +3329,7 @@
           <t>Tyeru</t>
         </is>
       </c>
-      <c r="B47" s="13" t="inlineStr">
+      <c r="B47" s="12" t="inlineStr">
         <is>
           <t>Warlock</t>
         </is>
@@ -3410,7 +3396,7 @@
           <t>Vityax</t>
         </is>
       </c>
-      <c r="B48" s="6" t="inlineStr">
+      <c r="B48" s="5" t="inlineStr">
         <is>
           <t>Hunter</t>
         </is>
@@ -3611,7 +3597,7 @@
           <t>Airunrsham</t>
         </is>
       </c>
-      <c r="B51" s="12" t="inlineStr">
+      <c r="B51" s="11" t="inlineStr">
         <is>
           <t>Shaman</t>
         </is>
@@ -3745,7 +3731,7 @@
           <t>Azrathiel</t>
         </is>
       </c>
-      <c r="B53" s="13" t="inlineStr">
+      <c r="B53" s="12" t="inlineStr">
         <is>
           <t>Warlock</t>
         </is>
@@ -3879,7 +3865,7 @@
           <t>Chalz</t>
         </is>
       </c>
-      <c r="B55" s="7" t="inlineStr">
+      <c r="B55" s="6" t="inlineStr">
         <is>
           <t>Mage</t>
         </is>
@@ -3946,7 +3932,7 @@
           <t>Demodin</t>
         </is>
       </c>
-      <c r="B56" s="13" t="inlineStr">
+      <c r="B56" s="12" t="inlineStr">
         <is>
           <t>Warlock</t>
         </is>
@@ -4013,7 +3999,7 @@
           <t>Dillery</t>
         </is>
       </c>
-      <c r="B57" s="11" t="inlineStr">
+      <c r="B57" s="10" t="inlineStr">
         <is>
           <t>Rogue</t>
         </is>
@@ -4080,7 +4066,7 @@
           <t>Domqq</t>
         </is>
       </c>
-      <c r="B58" s="9" t="inlineStr">
+      <c r="B58" s="8" t="inlineStr">
         <is>
           <t>Paladin</t>
         </is>
@@ -4147,7 +4133,7 @@
           <t>Draaxar</t>
         </is>
       </c>
-      <c r="B59" s="8" t="inlineStr">
+      <c r="B59" s="7" t="inlineStr">
         <is>
           <t>Monk</t>
         </is>
@@ -4214,7 +4200,7 @@
           <t>Erza</t>
         </is>
       </c>
-      <c r="B60" s="9" t="inlineStr">
+      <c r="B60" s="8" t="inlineStr">
         <is>
           <t>Paladin</t>
         </is>
@@ -4281,7 +4267,7 @@
           <t>Exa</t>
         </is>
       </c>
-      <c r="B61" s="7" t="inlineStr">
+      <c r="B61" s="6" t="inlineStr">
         <is>
           <t>Mage</t>
         </is>
@@ -4348,7 +4334,7 @@
           <t>Frog</t>
         </is>
       </c>
-      <c r="B62" s="11" t="inlineStr">
+      <c r="B62" s="10" t="inlineStr">
         <is>
           <t>Rogue</t>
         </is>
@@ -4415,7 +4401,7 @@
           <t>Gamêrgirl</t>
         </is>
       </c>
-      <c r="B63" s="7" t="inlineStr">
+      <c r="B63" s="6" t="inlineStr">
         <is>
           <t>Mage</t>
         </is>
@@ -4482,7 +4468,7 @@
           <t>Gerinctörés</t>
         </is>
       </c>
-      <c r="B64" s="10" t="inlineStr">
+      <c r="B64" s="9" t="inlineStr">
         <is>
           <t>Priest</t>
         </is>
@@ -4616,7 +4602,7 @@
           <t>Juu</t>
         </is>
       </c>
-      <c r="B66" s="7" t="inlineStr">
+      <c r="B66" s="6" t="inlineStr">
         <is>
           <t>Mage</t>
         </is>
@@ -4683,7 +4669,7 @@
           <t>Llýnch</t>
         </is>
       </c>
-      <c r="B67" s="10" t="inlineStr">
+      <c r="B67" s="9" t="inlineStr">
         <is>
           <t>Priest</t>
         </is>
@@ -4750,7 +4736,7 @@
           <t>Murungló</t>
         </is>
       </c>
-      <c r="B68" s="6" t="inlineStr">
+      <c r="B68" s="5" t="inlineStr">
         <is>
           <t>Hunter</t>
         </is>
@@ -4817,7 +4803,7 @@
           <t>Overhlmycrit</t>
         </is>
       </c>
-      <c r="B69" s="14" t="inlineStr">
+      <c r="B69" s="13" t="inlineStr">
         <is>
           <t>Warrior</t>
         </is>
@@ -4884,7 +4870,7 @@
           <t>Rileyreid</t>
         </is>
       </c>
-      <c r="B70" s="8" t="inlineStr">
+      <c r="B70" s="7" t="inlineStr">
         <is>
           <t>Monk</t>
         </is>
@@ -4951,7 +4937,7 @@
           <t>Sworly</t>
         </is>
       </c>
-      <c r="B71" s="12" t="inlineStr">
+      <c r="B71" s="11" t="inlineStr">
         <is>
           <t>Shaman</t>
         </is>
@@ -5018,7 +5004,7 @@
           <t>Trelhy</t>
         </is>
       </c>
-      <c r="B72" s="11" t="inlineStr">
+      <c r="B72" s="10" t="inlineStr">
         <is>
           <t>Rogue</t>
         </is>
@@ -5085,7 +5071,7 @@
           <t>Twiist</t>
         </is>
       </c>
-      <c r="B73" s="6" t="inlineStr">
+      <c r="B73" s="5" t="inlineStr">
         <is>
           <t>Hunter</t>
         </is>
@@ -5152,7 +5138,7 @@
           <t>Viomonkas</t>
         </is>
       </c>
-      <c r="B74" s="8" t="inlineStr">
+      <c r="B74" s="7" t="inlineStr">
         <is>
           <t>Monk</t>
         </is>
@@ -5353,7 +5339,7 @@
           <t>Aysta</t>
         </is>
       </c>
-      <c r="B77" s="10" t="inlineStr">
+      <c r="B77" s="9" t="inlineStr">
         <is>
           <t>Priest</t>
         </is>
@@ -5420,7 +5406,7 @@
           <t>Blinkmon</t>
         </is>
       </c>
-      <c r="B78" s="7" t="inlineStr">
+      <c r="B78" s="6" t="inlineStr">
         <is>
           <t>Mage</t>
         </is>
@@ -5554,7 +5540,7 @@
           <t>Brewby</t>
         </is>
       </c>
-      <c r="B80" s="8" t="inlineStr">
+      <c r="B80" s="7" t="inlineStr">
         <is>
           <t>Monk</t>
         </is>
@@ -5621,7 +5607,7 @@
           <t>Christensen</t>
         </is>
       </c>
-      <c r="B81" s="6" t="inlineStr">
+      <c r="B81" s="5" t="inlineStr">
         <is>
           <t>Hunter</t>
         </is>
@@ -5688,7 +5674,7 @@
           <t>Cornaith</t>
         </is>
       </c>
-      <c r="B82" s="13" t="inlineStr">
+      <c r="B82" s="12" t="inlineStr">
         <is>
           <t>Warlock</t>
         </is>
@@ -5822,7 +5808,7 @@
           <t>Deroxid</t>
         </is>
       </c>
-      <c r="B84" s="6" t="inlineStr">
+      <c r="B84" s="5" t="inlineStr">
         <is>
           <t>Hunter</t>
         </is>
@@ -5889,7 +5875,7 @@
           <t>Diambar</t>
         </is>
       </c>
-      <c r="B85" s="13" t="inlineStr">
+      <c r="B85" s="12" t="inlineStr">
         <is>
           <t>Warlock</t>
         </is>
@@ -5956,7 +5942,7 @@
           <t>Firefly</t>
         </is>
       </c>
-      <c r="B86" s="13" t="inlineStr">
+      <c r="B86" s="12" t="inlineStr">
         <is>
           <t>Warlock</t>
         </is>
@@ -6023,7 +6009,7 @@
           <t>Fuvesember</t>
         </is>
       </c>
-      <c r="B87" s="13" t="inlineStr">
+      <c r="B87" s="12" t="inlineStr">
         <is>
           <t>Warlock</t>
         </is>
@@ -6090,7 +6076,7 @@
           <t>Iramatide</t>
         </is>
       </c>
-      <c r="B88" s="12" t="inlineStr">
+      <c r="B88" s="11" t="inlineStr">
         <is>
           <t>Shaman</t>
         </is>
@@ -6157,7 +6143,7 @@
           <t>Istawizard</t>
         </is>
       </c>
-      <c r="B89" s="7" t="inlineStr">
+      <c r="B89" s="6" t="inlineStr">
         <is>
           <t>Mage</t>
         </is>
@@ -6224,7 +6210,7 @@
           <t>Life</t>
         </is>
       </c>
-      <c r="B90" s="6" t="inlineStr">
+      <c r="B90" s="5" t="inlineStr">
         <is>
           <t>Hunter</t>
         </is>
@@ -6291,7 +6277,7 @@
           <t>Lightraven</t>
         </is>
       </c>
-      <c r="B91" s="10" t="inlineStr">
+      <c r="B91" s="9" t="inlineStr">
         <is>
           <t>Priest</t>
         </is>
@@ -6358,7 +6344,7 @@
           <t>Mansoori</t>
         </is>
       </c>
-      <c r="B92" s="12" t="inlineStr">
+      <c r="B92" s="11" t="inlineStr">
         <is>
           <t>Shaman</t>
         </is>
@@ -6425,7 +6411,7 @@
           <t>Maviellian</t>
         </is>
       </c>
-      <c r="B93" s="6" t="inlineStr">
+      <c r="B93" s="5" t="inlineStr">
         <is>
           <t>Hunter</t>
         </is>
@@ -6492,7 +6478,7 @@
           <t>Meleepriest</t>
         </is>
       </c>
-      <c r="B94" s="10" t="inlineStr">
+      <c r="B94" s="9" t="inlineStr">
         <is>
           <t>Priest</t>
         </is>
@@ -6559,7 +6545,7 @@
           <t>Murlðck</t>
         </is>
       </c>
-      <c r="B95" s="13" t="inlineStr">
+      <c r="B95" s="12" t="inlineStr">
         <is>
           <t>Warlock</t>
         </is>
@@ -6626,7 +6612,7 @@
           <t>Neexmage</t>
         </is>
       </c>
-      <c r="B96" s="7" t="inlineStr">
+      <c r="B96" s="6" t="inlineStr">
         <is>
           <t>Mage</t>
         </is>
@@ -6693,7 +6679,7 @@
           <t>Neexmonk</t>
         </is>
       </c>
-      <c r="B97" s="8" t="inlineStr">
+      <c r="B97" s="7" t="inlineStr">
         <is>
           <t>Monk</t>
         </is>
@@ -6961,7 +6947,7 @@
           <t>Stormspear</t>
         </is>
       </c>
-      <c r="B101" s="6" t="inlineStr">
+      <c r="B101" s="5" t="inlineStr">
         <is>
           <t>Hunter</t>
         </is>
@@ -7028,7 +7014,7 @@
           <t>Swextor</t>
         </is>
       </c>
-      <c r="B102" s="12" t="inlineStr">
+      <c r="B102" s="11" t="inlineStr">
         <is>
           <t>Shaman</t>
         </is>
@@ -7095,7 +7081,7 @@
           <t>Voidspriest</t>
         </is>
       </c>
-      <c r="B103" s="10" t="inlineStr">
+      <c r="B103" s="9" t="inlineStr">
         <is>
           <t>Priest</t>
         </is>
@@ -7162,7 +7148,7 @@
           <t>Wetanus</t>
         </is>
       </c>
-      <c r="B104" s="9" t="inlineStr">
+      <c r="B104" s="8" t="inlineStr">
         <is>
           <t>Paladin</t>
         </is>
@@ -7229,7 +7215,7 @@
           <t>Xayton</t>
         </is>
       </c>
-      <c r="B105" s="14" t="inlineStr">
+      <c r="B105" s="13" t="inlineStr">
         <is>
           <t>Warrior</t>
         </is>
@@ -7296,7 +7282,7 @@
           <t>Zigolera</t>
         </is>
       </c>
-      <c r="B106" s="11" t="inlineStr">
+      <c r="B106" s="10" t="inlineStr">
         <is>
           <t>Rogue</t>
         </is>
@@ -7363,7 +7349,7 @@
           <t>Zumwanti</t>
         </is>
       </c>
-      <c r="B107" s="7" t="inlineStr">
+      <c r="B107" s="6" t="inlineStr">
         <is>
           <t>Mage</t>
         </is>
@@ -7430,7 +7416,7 @@
           <t>Csodafa</t>
         </is>
       </c>
-      <c r="B108" s="12" t="inlineStr">
+      <c r="B108" s="11" t="inlineStr">
         <is>
           <t>Shaman</t>
         </is>
@@ -7497,7 +7483,7 @@
           <t>Joeqq</t>
         </is>
       </c>
-      <c r="B109" s="8" t="inlineStr">
+      <c r="B109" s="7" t="inlineStr">
         <is>
           <t>Monk</t>
         </is>
@@ -7564,7 +7550,7 @@
           <t>Ktyafej</t>
         </is>
       </c>
-      <c r="B110" s="13" t="inlineStr">
+      <c r="B110" s="12" t="inlineStr">
         <is>
           <t>Warlock</t>
         </is>
@@ -7631,7 +7617,7 @@
           <t>Lqd</t>
         </is>
       </c>
-      <c r="B111" s="11" t="inlineStr">
+      <c r="B111" s="10" t="inlineStr">
         <is>
           <t>Rogue</t>
         </is>
@@ -7698,7 +7684,7 @@
           <t>Mocsarpuna</t>
         </is>
       </c>
-      <c r="B112" s="14" t="inlineStr">
+      <c r="B112" s="13" t="inlineStr">
         <is>
           <t>Warrior</t>
         </is>
@@ -7765,7 +7751,7 @@
           <t>Olcsojatek</t>
         </is>
       </c>
-      <c r="B113" s="7" t="inlineStr">
+      <c r="B113" s="6" t="inlineStr">
         <is>
           <t>Mage</t>
         </is>
@@ -7832,7 +7818,7 @@
           <t>Pisswater</t>
         </is>
       </c>
-      <c r="B114" s="12" t="inlineStr">
+      <c r="B114" s="11" t="inlineStr">
         <is>
           <t>Shaman</t>
         </is>
@@ -7899,7 +7885,7 @@
           <t>Rastaeri</t>
         </is>
       </c>
-      <c r="B115" s="14" t="inlineStr">
+      <c r="B115" s="13" t="inlineStr">
         <is>
           <t>Warrior</t>
         </is>
@@ -7966,7 +7952,7 @@
           <t>Shadis</t>
         </is>
       </c>
-      <c r="B116" s="11" t="inlineStr">
+      <c r="B116" s="10" t="inlineStr">
         <is>
           <t>Rogue</t>
         </is>
@@ -8100,7 +8086,7 @@
           <t>Zawø</t>
         </is>
       </c>
-      <c r="B118" s="8" t="inlineStr">
+      <c r="B118" s="7" t="inlineStr">
         <is>
           <t>Monk</t>
         </is>
@@ -8167,7 +8153,7 @@
           <t>Åzkareth</t>
         </is>
       </c>
-      <c r="B119" s="13" t="inlineStr">
+      <c r="B119" s="12" t="inlineStr">
         <is>
           <t>Warlock</t>
         </is>
@@ -8234,7 +8220,7 @@
           <t>ßehro</t>
         </is>
       </c>
-      <c r="B120" s="8" t="inlineStr">
+      <c r="B120" s="7" t="inlineStr">
         <is>
           <t>Monk</t>
         </is>
@@ -8301,7 +8287,7 @@
           <t>Alinalopez</t>
         </is>
       </c>
-      <c r="B121" s="14" t="inlineStr">
+      <c r="B121" s="13" t="inlineStr">
         <is>
           <t>Warrior</t>
         </is>
@@ -8368,7 +8354,7 @@
           <t>Azeela</t>
         </is>
       </c>
-      <c r="B122" s="7" t="inlineStr">
+      <c r="B122" s="6" t="inlineStr">
         <is>
           <t>Mage</t>
         </is>
@@ -8435,7 +8421,7 @@
           <t>Aztahey</t>
         </is>
       </c>
-      <c r="B123" s="7" t="inlineStr">
+      <c r="B123" s="6" t="inlineStr">
         <is>
           <t>Mage</t>
         </is>
@@ -8502,7 +8488,7 @@
           <t>Aztahé</t>
         </is>
       </c>
-      <c r="B124" s="8" t="inlineStr">
+      <c r="B124" s="7" t="inlineStr">
         <is>
           <t>Monk</t>
         </is>
@@ -8569,7 +8555,7 @@
           <t>Babjin</t>
         </is>
       </c>
-      <c r="B125" s="6" t="inlineStr">
+      <c r="B125" s="5" t="inlineStr">
         <is>
           <t>Hunter</t>
         </is>
@@ -8636,7 +8622,7 @@
           <t>Blackyng</t>
         </is>
       </c>
-      <c r="B126" s="7" t="inlineStr">
+      <c r="B126" s="6" t="inlineStr">
         <is>
           <t>Mage</t>
         </is>
@@ -8703,7 +8689,7 @@
           <t>Brema</t>
         </is>
       </c>
-      <c r="B127" s="7" t="inlineStr">
+      <c r="B127" s="6" t="inlineStr">
         <is>
           <t>Mage</t>
         </is>
@@ -8904,7 +8890,7 @@
           <t>Caisbro</t>
         </is>
       </c>
-      <c r="B130" s="10" t="inlineStr">
+      <c r="B130" s="9" t="inlineStr">
         <is>
           <t>Priest</t>
         </is>
@@ -9172,7 +9158,7 @@
           <t>Clenyo</t>
         </is>
       </c>
-      <c r="B134" s="10" t="inlineStr">
+      <c r="B134" s="9" t="inlineStr">
         <is>
           <t>Priest</t>
         </is>
@@ -9239,7 +9225,7 @@
           <t>Constermock</t>
         </is>
       </c>
-      <c r="B135" s="9" t="inlineStr">
+      <c r="B135" s="8" t="inlineStr">
         <is>
           <t>Paladin</t>
         </is>
@@ -9306,7 +9292,7 @@
           <t>Culyka</t>
         </is>
       </c>
-      <c r="B136" s="13" t="inlineStr">
+      <c r="B136" s="12" t="inlineStr">
         <is>
           <t>Warlock</t>
         </is>
@@ -9373,7 +9359,7 @@
           <t>Daddykasta</t>
         </is>
       </c>
-      <c r="B137" s="6" t="inlineStr">
+      <c r="B137" s="5" t="inlineStr">
         <is>
           <t>Hunter</t>
         </is>
@@ -9440,7 +9426,7 @@
           <t>Deathdealing</t>
         </is>
       </c>
-      <c r="B138" s="11" t="inlineStr">
+      <c r="B138" s="10" t="inlineStr">
         <is>
           <t>Rogue</t>
         </is>
@@ -9574,7 +9560,7 @@
           <t>Doelen</t>
         </is>
       </c>
-      <c r="B140" s="10" t="inlineStr">
+      <c r="B140" s="9" t="inlineStr">
         <is>
           <t>Priest</t>
         </is>
@@ -9641,7 +9627,7 @@
           <t>Exà</t>
         </is>
       </c>
-      <c r="B141" s="11" t="inlineStr">
+      <c r="B141" s="10" t="inlineStr">
         <is>
           <t>Rogue</t>
         </is>
@@ -9708,7 +9694,7 @@
           <t>Exã</t>
         </is>
       </c>
-      <c r="B142" s="12" t="inlineStr">
+      <c r="B142" s="11" t="inlineStr">
         <is>
           <t>Shaman</t>
         </is>
@@ -9775,7 +9761,7 @@
           <t>Exå</t>
         </is>
       </c>
-      <c r="B143" s="9" t="inlineStr">
+      <c r="B143" s="8" t="inlineStr">
         <is>
           <t>Paladin</t>
         </is>
@@ -9842,7 +9828,7 @@
           <t>Frost</t>
         </is>
       </c>
-      <c r="B144" s="7" t="inlineStr">
+      <c r="B144" s="6" t="inlineStr">
         <is>
           <t>Mage</t>
         </is>
@@ -9909,7 +9895,7 @@
           <t>Fruell</t>
         </is>
       </c>
-      <c r="B145" s="8" t="inlineStr">
+      <c r="B145" s="7" t="inlineStr">
         <is>
           <t>Monk</t>
         </is>
@@ -10110,7 +10096,7 @@
           <t>Hering</t>
         </is>
       </c>
-      <c r="B148" s="12" t="inlineStr">
+      <c r="B148" s="11" t="inlineStr">
         <is>
           <t>Shaman</t>
         </is>
@@ -10177,7 +10163,7 @@
           <t>Hesing</t>
         </is>
       </c>
-      <c r="B149" s="9" t="inlineStr">
+      <c r="B149" s="8" t="inlineStr">
         <is>
           <t>Paladin</t>
         </is>
@@ -10378,7 +10364,7 @@
           <t>Hesnxg</t>
         </is>
       </c>
-      <c r="B152" s="11" t="inlineStr">
+      <c r="B152" s="10" t="inlineStr">
         <is>
           <t>Rogue</t>
         </is>
@@ -10445,7 +10431,7 @@
           <t>Hxsxng</t>
         </is>
       </c>
-      <c r="B153" s="7" t="inlineStr">
+      <c r="B153" s="6" t="inlineStr">
         <is>
           <t>Mage</t>
         </is>
@@ -10512,7 +10498,7 @@
           <t>Hêsing</t>
         </is>
       </c>
-      <c r="B154" s="9" t="inlineStr">
+      <c r="B154" s="8" t="inlineStr">
         <is>
           <t>Paladin</t>
         </is>
@@ -10579,7 +10565,7 @@
           <t>Imlock</t>
         </is>
       </c>
-      <c r="B155" s="13" t="inlineStr">
+      <c r="B155" s="12" t="inlineStr">
         <is>
           <t>Warlock</t>
         </is>
@@ -10646,7 +10632,7 @@
           <t>Istawarr</t>
         </is>
       </c>
-      <c r="B156" s="14" t="inlineStr">
+      <c r="B156" s="13" t="inlineStr">
         <is>
           <t>Warrior</t>
         </is>
@@ -10780,7 +10766,7 @@
           <t>Kaiser</t>
         </is>
       </c>
-      <c r="B158" s="14" t="inlineStr">
+      <c r="B158" s="13" t="inlineStr">
         <is>
           <t>Warrior</t>
         </is>
@@ -10847,7 +10833,7 @@
           <t>Kastablasta</t>
         </is>
       </c>
-      <c r="B159" s="9" t="inlineStr">
+      <c r="B159" s="8" t="inlineStr">
         <is>
           <t>Paladin</t>
         </is>
@@ -10981,7 +10967,7 @@
           <t>Kastaegurl</t>
         </is>
       </c>
-      <c r="B161" s="11" t="inlineStr">
+      <c r="B161" s="10" t="inlineStr">
         <is>
           <t>Rogue</t>
         </is>
@@ -11048,7 +11034,7 @@
           <t>Kastajutsu</t>
         </is>
       </c>
-      <c r="B162" s="12" t="inlineStr">
+      <c r="B162" s="11" t="inlineStr">
         <is>
           <t>Shaman</t>
         </is>
@@ -11115,7 +11101,7 @@
           <t>Kastalynn</t>
         </is>
       </c>
-      <c r="B163" s="10" t="inlineStr">
+      <c r="B163" s="9" t="inlineStr">
         <is>
           <t>Priest</t>
         </is>
@@ -11182,7 +11168,7 @@
           <t>Kastameow</t>
         </is>
       </c>
-      <c r="B164" s="10" t="inlineStr">
+      <c r="B164" s="9" t="inlineStr">
         <is>
           <t>Priest</t>
         </is>
@@ -11316,7 +11302,7 @@
           <t>Kastayaya</t>
         </is>
       </c>
-      <c r="B166" s="7" t="inlineStr">
+      <c r="B166" s="6" t="inlineStr">
         <is>
           <t>Mage</t>
         </is>
@@ -11383,7 +11369,7 @@
           <t>Killapete</t>
         </is>
       </c>
-      <c r="B167" s="12" t="inlineStr">
+      <c r="B167" s="11" t="inlineStr">
         <is>
           <t>Shaman</t>
         </is>
@@ -11450,7 +11436,7 @@
           <t>Kwaygon</t>
         </is>
       </c>
-      <c r="B168" s="8" t="inlineStr">
+      <c r="B168" s="7" t="inlineStr">
         <is>
           <t>Monk</t>
         </is>
@@ -11517,7 +11503,7 @@
           <t>Kygän</t>
         </is>
       </c>
-      <c r="B169" s="14" t="inlineStr">
+      <c r="B169" s="13" t="inlineStr">
         <is>
           <t>Warrior</t>
         </is>
@@ -11584,7 +11570,7 @@
           <t>Lightwithinx</t>
         </is>
       </c>
-      <c r="B170" s="10" t="inlineStr">
+      <c r="B170" s="9" t="inlineStr">
         <is>
           <t>Priest</t>
         </is>
@@ -11651,7 +11637,7 @@
           <t>Mcfrizzle</t>
         </is>
       </c>
-      <c r="B171" s="7" t="inlineStr">
+      <c r="B171" s="6" t="inlineStr">
         <is>
           <t>Mage</t>
         </is>
@@ -11718,7 +11704,7 @@
           <t>Monkaqts</t>
         </is>
       </c>
-      <c r="B172" s="8" t="inlineStr">
+      <c r="B172" s="7" t="inlineStr">
         <is>
           <t>Monk</t>
         </is>
@@ -11852,7 +11838,7 @@
           <t>Notvenz</t>
         </is>
       </c>
-      <c r="B174" s="6" t="inlineStr">
+      <c r="B174" s="5" t="inlineStr">
         <is>
           <t>Hunter</t>
         </is>
@@ -11986,7 +11972,7 @@
           <t>Pisspriest</t>
         </is>
       </c>
-      <c r="B176" s="10" t="inlineStr">
+      <c r="B176" s="9" t="inlineStr">
         <is>
           <t>Priest</t>
         </is>
@@ -12053,7 +12039,7 @@
           <t>Popegodx</t>
         </is>
       </c>
-      <c r="B177" s="10" t="inlineStr">
+      <c r="B177" s="9" t="inlineStr">
         <is>
           <t>Priest</t>
         </is>
@@ -12120,7 +12106,7 @@
           <t>Rewriight</t>
         </is>
       </c>
-      <c r="B178" s="8" t="inlineStr">
+      <c r="B178" s="7" t="inlineStr">
         <is>
           <t>Monk</t>
         </is>
@@ -12187,7 +12173,7 @@
           <t>Rewrlght</t>
         </is>
       </c>
-      <c r="B179" s="6" t="inlineStr">
+      <c r="B179" s="5" t="inlineStr">
         <is>
           <t>Hunter</t>
         </is>
@@ -12321,7 +12307,7 @@
           <t>Rewryght</t>
         </is>
       </c>
-      <c r="B181" s="8" t="inlineStr">
+      <c r="B181" s="7" t="inlineStr">
         <is>
           <t>Monk</t>
         </is>
@@ -12455,7 +12441,7 @@
           <t>Rhaenys</t>
         </is>
       </c>
-      <c r="B183" s="7" t="inlineStr">
+      <c r="B183" s="6" t="inlineStr">
         <is>
           <t>Mage</t>
         </is>
@@ -12522,7 +12508,7 @@
           <t>Shadís</t>
         </is>
       </c>
-      <c r="B184" s="7" t="inlineStr">
+      <c r="B184" s="6" t="inlineStr">
         <is>
           <t>Mage</t>
         </is>
@@ -12589,7 +12575,7 @@
           <t>Skillnova</t>
         </is>
       </c>
-      <c r="B185" s="12" t="inlineStr">
+      <c r="B185" s="11" t="inlineStr">
         <is>
           <t>Shaman</t>
         </is>
@@ -12723,7 +12709,7 @@
           <t>Skoghunt</t>
         </is>
       </c>
-      <c r="B187" s="6" t="inlineStr">
+      <c r="B187" s="5" t="inlineStr">
         <is>
           <t>Hunter</t>
         </is>
@@ -12790,7 +12776,7 @@
           <t>Sophierain</t>
         </is>
       </c>
-      <c r="B188" s="8" t="inlineStr">
+      <c r="B188" s="7" t="inlineStr">
         <is>
           <t>Monk</t>
         </is>
@@ -12924,7 +12910,7 @@
           <t>Ssjkasta</t>
         </is>
       </c>
-      <c r="B190" s="13" t="inlineStr">
+      <c r="B190" s="12" t="inlineStr">
         <is>
           <t>Warlock</t>
         </is>
@@ -13058,7 +13044,7 @@
           <t>Stareyess</t>
         </is>
       </c>
-      <c r="B192" s="9" t="inlineStr">
+      <c r="B192" s="8" t="inlineStr">
         <is>
           <t>Paladin</t>
         </is>
@@ -13125,7 +13111,7 @@
           <t>Subenjoyer</t>
         </is>
       </c>
-      <c r="B193" s="11" t="inlineStr">
+      <c r="B193" s="10" t="inlineStr">
         <is>
           <t>Rogue</t>
         </is>
@@ -13192,7 +13178,7 @@
           <t>Svetovid</t>
         </is>
       </c>
-      <c r="B194" s="14" t="inlineStr">
+      <c r="B194" s="13" t="inlineStr">
         <is>
           <t>Warrior</t>
         </is>
@@ -13393,7 +13379,7 @@
           <t>Tyerurape</t>
         </is>
       </c>
-      <c r="B197" s="7" t="inlineStr">
+      <c r="B197" s="6" t="inlineStr">
         <is>
           <t>Mage</t>
         </is>
@@ -13460,7 +13446,7 @@
           <t>Tyeruyay</t>
         </is>
       </c>
-      <c r="B198" s="8" t="inlineStr">
+      <c r="B198" s="7" t="inlineStr">
         <is>
           <t>Monk</t>
         </is>
@@ -13661,7 +13647,7 @@
           <t>Urtrik</t>
         </is>
       </c>
-      <c r="B201" s="14" t="inlineStr">
+      <c r="B201" s="13" t="inlineStr">
         <is>
           <t>Warrior</t>
         </is>
@@ -13728,7 +13714,7 @@
           <t>Venz</t>
         </is>
       </c>
-      <c r="B202" s="8" t="inlineStr">
+      <c r="B202" s="7" t="inlineStr">
         <is>
           <t>Monk</t>
         </is>
@@ -13862,7 +13848,7 @@
           <t>Venzy</t>
         </is>
       </c>
-      <c r="B204" s="9" t="inlineStr">
+      <c r="B204" s="8" t="inlineStr">
         <is>
           <t>Paladin</t>
         </is>
@@ -13929,7 +13915,7 @@
           <t>Venømm</t>
         </is>
       </c>
-      <c r="B205" s="6" t="inlineStr">
+      <c r="B205" s="5" t="inlineStr">
         <is>
           <t>Hunter</t>
         </is>
@@ -13996,7 +13982,7 @@
           <t>Vityadisc</t>
         </is>
       </c>
-      <c r="B206" s="10" t="inlineStr">
+      <c r="B206" s="9" t="inlineStr">
         <is>
           <t>Priest</t>
         </is>
@@ -14063,7 +14049,7 @@
           <t>Vityaex</t>
         </is>
       </c>
-      <c r="B207" s="7" t="inlineStr">
+      <c r="B207" s="6" t="inlineStr">
         <is>
           <t>Mage</t>
         </is>
@@ -14197,7 +14183,7 @@
           <t>Vityatm</t>
         </is>
       </c>
-      <c r="B209" s="13" t="inlineStr">
+      <c r="B209" s="12" t="inlineStr">
         <is>
           <t>Warlock</t>
         </is>
@@ -14264,7 +14250,7 @@
           <t>Vityatx</t>
         </is>
       </c>
-      <c r="B210" s="9" t="inlineStr">
+      <c r="B210" s="8" t="inlineStr">
         <is>
           <t>Paladin</t>
         </is>
@@ -14331,7 +14317,7 @@
           <t>Vityaw</t>
         </is>
       </c>
-      <c r="B211" s="11" t="inlineStr">
+      <c r="B211" s="10" t="inlineStr">
         <is>
           <t>Rogue</t>
         </is>
@@ -14398,7 +14384,7 @@
           <t>Vityaxarms</t>
         </is>
       </c>
-      <c r="B212" s="14" t="inlineStr">
+      <c r="B212" s="13" t="inlineStr">
         <is>
           <t>Warrior</t>
         </is>
@@ -14532,7 +14518,7 @@
           <t>Vityaxt</t>
         </is>
       </c>
-      <c r="B214" s="12" t="inlineStr">
+      <c r="B214" s="11" t="inlineStr">
         <is>
           <t>Shaman</t>
         </is>
@@ -14599,7 +14585,7 @@
           <t>Vénz</t>
         </is>
       </c>
-      <c r="B215" s="13" t="inlineStr">
+      <c r="B215" s="12" t="inlineStr">
         <is>
           <t>Warlock</t>
         </is>
@@ -14666,7 +14652,7 @@
           <t>Wazakutyám</t>
         </is>
       </c>
-      <c r="B216" s="14" t="inlineStr">
+      <c r="B216" s="13" t="inlineStr">
         <is>
           <t>Warrior</t>
         </is>
@@ -14733,7 +14719,7 @@
           <t>Webway</t>
         </is>
       </c>
-      <c r="B217" s="13" t="inlineStr">
+      <c r="B217" s="12" t="inlineStr">
         <is>
           <t>Warlock</t>
         </is>
@@ -14867,7 +14853,7 @@
           <t>Whiskyjárat</t>
         </is>
       </c>
-      <c r="B219" s="7" t="inlineStr">
+      <c r="B219" s="6" t="inlineStr">
         <is>
           <t>Mage</t>
         </is>
@@ -14934,7 +14920,7 @@
           <t>Wooj</t>
         </is>
       </c>
-      <c r="B220" s="7" t="inlineStr">
+      <c r="B220" s="6" t="inlineStr">
         <is>
           <t>Mage</t>
         </is>
@@ -15001,7 +14987,7 @@
           <t>Worldsbest</t>
         </is>
       </c>
-      <c r="B221" s="14" t="inlineStr">
+      <c r="B221" s="13" t="inlineStr">
         <is>
           <t>Warrior</t>
         </is>
@@ -15135,7 +15121,7 @@
           <t>Wzp</t>
         </is>
       </c>
-      <c r="B223" s="10" t="inlineStr">
+      <c r="B223" s="9" t="inlineStr">
         <is>
           <t>Priest</t>
         </is>
@@ -15202,7 +15188,7 @@
           <t>Wäkkä</t>
         </is>
       </c>
-      <c r="B224" s="10" t="inlineStr">
+      <c r="B224" s="9" t="inlineStr">
         <is>
           <t>Priest</t>
         </is>
@@ -15269,7 +15255,7 @@
           <t>Yodawar</t>
         </is>
       </c>
-      <c r="B225" s="14" t="inlineStr">
+      <c r="B225" s="13" t="inlineStr">
         <is>
           <t>Warrior</t>
         </is>
@@ -15336,7 +15322,7 @@
           <t>Zendino</t>
         </is>
       </c>
-      <c r="B226" s="8" t="inlineStr">
+      <c r="B226" s="7" t="inlineStr">
         <is>
           <t>Monk</t>
         </is>
@@ -15604,7 +15590,7 @@
           <t>Åether</t>
         </is>
       </c>
-      <c r="B230" s="11" t="inlineStr">
+      <c r="B230" s="10" t="inlineStr">
         <is>
           <t>Rogue</t>
         </is>
